--- a/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
+++ b/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="172">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -750,7 +750,13 @@
     <t>Exception (IAE)</t>
   </si>
   <si>
-    <t>da</t>
+    <t>67% line, 100% brach</t>
+  </si>
+  <si>
+    <t>nu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nu am găsit niciun bug în codul funcției </t>
   </si>
 </sst>
 </file>
@@ -1571,6 +1577,30 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1580,74 +1610,110 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1658,6 +1724,18 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1670,18 +1748,60 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1691,128 +1811,14 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2215,12 +2221,12 @@
   <sheetData>
     <row r="1" spans="2:17">
       <c r="B1" s="12"/>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="42"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="50"/>
     </row>
     <row r="2" spans="2:17">
       <c r="B2" s="37" t="s">
@@ -2369,73 +2375,73 @@
   <sheetData>
     <row r="1" spans="2:20">
       <c r="B1" s="12"/>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="42"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="50"/>
     </row>
     <row r="3" spans="2:20" ht="16.8" customHeight="1">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="55" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="51"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="6" spans="2:20">
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="42"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="50"/>
       <c r="F6" s="29"/>
       <c r="G6" s="29"/>
-      <c r="I6" s="40" t="s">
+      <c r="I6" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="Q6" s="40" t="s">
+      <c r="J6" s="49"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="49"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="49"/>
+      <c r="Q6" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="R6" s="41"/>
-      <c r="S6" s="41"/>
-      <c r="T6" s="41"/>
+      <c r="R6" s="49"/>
+      <c r="S6" s="49"/>
+      <c r="T6" s="49"/>
     </row>
     <row r="8" spans="2:20">
       <c r="B8" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="57" t="s">
+      <c r="C8" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
       <c r="F8" s="31"/>
       <c r="G8" s="31"/>
       <c r="I8" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="Q8" s="45" t="s">
+      <c r="Q8" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="R8" s="45"/>
-      <c r="S8" s="45"/>
+      <c r="R8" s="65"/>
+      <c r="S8" s="65"/>
       <c r="T8" s="32">
         <v>6</v>
       </c>
@@ -2444,20 +2450,20 @@
       <c r="B9" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="58" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
       <c r="I9" s="36"/>
-      <c r="Q9" s="45" t="s">
+      <c r="Q9" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="R9" s="45"/>
-      <c r="S9" s="45"/>
-      <c r="T9" s="100" t="s">
+      <c r="R9" s="65"/>
+      <c r="S9" s="65"/>
+      <c r="T9" s="40" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2465,30 +2471,30 @@
       <c r="B10" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="44" t="s">
+      <c r="C10" s="58" t="s">
         <v>95</v>
       </c>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
       <c r="F10" s="34"/>
       <c r="G10" s="34"/>
-      <c r="I10" s="52" t="s">
+      <c r="I10" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="53"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="54"/>
-      <c r="Q10" s="45" t="s">
+      <c r="J10" s="60"/>
+      <c r="K10" s="60"/>
+      <c r="L10" s="60"/>
+      <c r="M10" s="60"/>
+      <c r="N10" s="60"/>
+      <c r="O10" s="61"/>
+      <c r="Q10" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="R10" s="45" t="s">
+      <c r="R10" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="S10" s="45"/>
-      <c r="T10" s="100" t="s">
+      <c r="S10" s="65"/>
+      <c r="T10" s="40" t="s">
         <v>107</v>
       </c>
     </row>
@@ -2496,283 +2502,286 @@
       <c r="B11" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="44" t="s">
+      <c r="C11" s="58" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
       <c r="F11" s="34"/>
       <c r="G11" s="34"/>
-      <c r="I11" s="55"/>
-      <c r="J11" s="99"/>
-      <c r="K11" s="99"/>
-      <c r="L11" s="99"/>
-      <c r="M11" s="99"/>
-      <c r="N11" s="99"/>
-      <c r="O11" s="56"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="63"/>
+      <c r="K11" s="63"/>
+      <c r="L11" s="63"/>
+      <c r="M11" s="63"/>
+      <c r="N11" s="63"/>
+      <c r="O11" s="64"/>
     </row>
     <row r="12" spans="2:20">
       <c r="B12" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="C12" s="44" t="s">
+      <c r="C12" s="58" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
       <c r="F12" s="34"/>
       <c r="G12" s="34"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="99"/>
-      <c r="K12" s="99"/>
-      <c r="L12" s="99"/>
-      <c r="M12" s="99"/>
-      <c r="N12" s="99"/>
-      <c r="O12" s="56"/>
+      <c r="I12" s="62"/>
+      <c r="J12" s="63"/>
+      <c r="K12" s="63"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="63"/>
+      <c r="O12" s="64"/>
     </row>
     <row r="13" spans="2:20">
       <c r="B13" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="44" t="s">
+      <c r="C13" s="58" t="s">
         <v>98</v>
       </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="58"/>
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="99"/>
-      <c r="K13" s="99"/>
-      <c r="L13" s="99"/>
-      <c r="M13" s="99"/>
-      <c r="N13" s="99"/>
-      <c r="O13" s="56"/>
-      <c r="Q13" s="40" t="s">
+      <c r="I13" s="62"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="63"/>
+      <c r="L13" s="63"/>
+      <c r="M13" s="63"/>
+      <c r="N13" s="63"/>
+      <c r="O13" s="64"/>
+      <c r="Q13" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="R13" s="41"/>
-      <c r="S13" s="41"/>
-      <c r="T13" s="41"/>
+      <c r="R13" s="49"/>
+      <c r="S13" s="49"/>
+      <c r="T13" s="49"/>
     </row>
     <row r="14" spans="2:20">
       <c r="B14" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="58" t="s">
         <v>99</v>
       </c>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
       <c r="F14" s="34"/>
       <c r="G14" s="34"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="99"/>
-      <c r="K14" s="99"/>
-      <c r="L14" s="99"/>
-      <c r="M14" s="99"/>
-      <c r="N14" s="99"/>
-      <c r="O14" s="56"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="63"/>
+      <c r="K14" s="63"/>
+      <c r="L14" s="63"/>
+      <c r="M14" s="63"/>
+      <c r="N14" s="63"/>
+      <c r="O14" s="64"/>
     </row>
     <row r="15" spans="2:20">
       <c r="B15" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="46" t="s">
+      <c r="C15" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="D15" s="47"/>
-      <c r="E15" s="48"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="99"/>
-      <c r="K15" s="99"/>
-      <c r="L15" s="99"/>
-      <c r="M15" s="99"/>
-      <c r="N15" s="99"/>
-      <c r="O15" s="56"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="53"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="63"/>
+      <c r="L15" s="63"/>
+      <c r="M15" s="63"/>
+      <c r="N15" s="63"/>
+      <c r="O15" s="64"/>
       <c r="Q15" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="R15" s="57" t="s">
+      <c r="R15" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="S15" s="57"/>
-      <c r="T15" s="57"/>
+      <c r="S15" s="66"/>
+      <c r="T15" s="66"/>
     </row>
     <row r="16" spans="2:20">
       <c r="B16" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C16" s="46" t="s">
+      <c r="C16" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="47"/>
-      <c r="E16" s="48"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="99"/>
-      <c r="K16" s="99"/>
-      <c r="L16" s="99"/>
-      <c r="M16" s="99"/>
-      <c r="N16" s="99"/>
-      <c r="O16" s="56"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="53"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="63"/>
+      <c r="K16" s="63"/>
+      <c r="L16" s="63"/>
+      <c r="M16" s="63"/>
+      <c r="N16" s="63"/>
+      <c r="O16" s="64"/>
       <c r="Q16" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="R16" s="43" t="s">
+      <c r="R16" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="S16" s="43"/>
-      <c r="T16" s="43"/>
+      <c r="S16" s="54"/>
+      <c r="T16" s="54"/>
     </row>
     <row r="17" spans="2:20">
       <c r="B17" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="46" t="s">
+      <c r="C17" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D17" s="47"/>
-      <c r="E17" s="48"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="99"/>
-      <c r="K17" s="99"/>
-      <c r="L17" s="99"/>
-      <c r="M17" s="99"/>
-      <c r="N17" s="99"/>
-      <c r="O17" s="56"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="53"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="63"/>
+      <c r="L17" s="63"/>
+      <c r="M17" s="63"/>
+      <c r="N17" s="63"/>
+      <c r="O17" s="64"/>
       <c r="Q17" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="R17" s="43" t="s">
+      <c r="R17" s="54" t="s">
         <v>113</v>
       </c>
-      <c r="S17" s="43"/>
-      <c r="T17" s="43"/>
+      <c r="S17" s="54"/>
+      <c r="T17" s="54"/>
     </row>
     <row r="18" spans="2:20">
       <c r="B18" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="46" t="s">
+      <c r="C18" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="D18" s="47"/>
-      <c r="E18" s="48"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="99"/>
-      <c r="K18" s="99"/>
-      <c r="L18" s="99"/>
-      <c r="M18" s="99"/>
-      <c r="N18" s="99"/>
-      <c r="O18" s="56"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="53"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="63"/>
+      <c r="K18" s="63"/>
+      <c r="L18" s="63"/>
+      <c r="M18" s="63"/>
+      <c r="N18" s="63"/>
+      <c r="O18" s="64"/>
       <c r="Q18" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="R18" s="43" t="s">
+      <c r="R18" s="54" t="s">
         <v>114</v>
       </c>
-      <c r="S18" s="43"/>
-      <c r="T18" s="43"/>
+      <c r="S18" s="54"/>
+      <c r="T18" s="54"/>
     </row>
     <row r="19" spans="2:20">
       <c r="B19" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="C19" s="46" t="s">
+      <c r="C19" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="D19" s="47"/>
-      <c r="E19" s="48"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="99"/>
-      <c r="K19" s="99"/>
-      <c r="L19" s="99"/>
-      <c r="M19" s="99"/>
-      <c r="N19" s="99"/>
-      <c r="O19" s="56"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="53"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="63"/>
+      <c r="L19" s="63"/>
+      <c r="M19" s="63"/>
+      <c r="N19" s="63"/>
+      <c r="O19" s="64"/>
       <c r="Q19" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="R19" s="43" t="s">
+      <c r="R19" s="54" t="s">
         <v>115</v>
       </c>
-      <c r="S19" s="43"/>
-      <c r="T19" s="43"/>
+      <c r="S19" s="54"/>
+      <c r="T19" s="54"/>
     </row>
     <row r="20" spans="2:20">
       <c r="B20" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="46" t="s">
+      <c r="C20" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="D20" s="47"/>
-      <c r="E20" s="48"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="99"/>
-      <c r="K20" s="99"/>
-      <c r="L20" s="99"/>
-      <c r="M20" s="99"/>
-      <c r="N20" s="99"/>
-      <c r="O20" s="56"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="53"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="63"/>
+      <c r="K20" s="63"/>
+      <c r="L20" s="63"/>
+      <c r="M20" s="63"/>
+      <c r="N20" s="63"/>
+      <c r="O20" s="64"/>
       <c r="Q20" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="R20" s="43" t="s">
+      <c r="R20" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="S20" s="43"/>
-      <c r="T20" s="43"/>
+      <c r="S20" s="54"/>
+      <c r="T20" s="54"/>
     </row>
     <row r="21" spans="2:20">
       <c r="B21" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="46" t="s">
+      <c r="C21" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="D21" s="47"/>
-      <c r="E21" s="48"/>
-      <c r="I21" s="55"/>
-      <c r="J21" s="99"/>
-      <c r="K21" s="99"/>
-      <c r="L21" s="99"/>
-      <c r="M21" s="99"/>
-      <c r="N21" s="99"/>
-      <c r="O21" s="56"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="53"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="63"/>
+      <c r="K21" s="63"/>
+      <c r="L21" s="63"/>
+      <c r="M21" s="63"/>
+      <c r="N21" s="63"/>
+      <c r="O21" s="64"/>
       <c r="Q21" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="R21" s="43" t="s">
+      <c r="R21" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="S21" s="43"/>
-      <c r="T21" s="43"/>
+      <c r="S21" s="54"/>
+      <c r="T21" s="54"/>
     </row>
     <row r="22" spans="2:20">
       <c r="B22" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="47"/>
-      <c r="E22" s="48"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="99"/>
-      <c r="K22" s="99"/>
-      <c r="L22" s="99"/>
-      <c r="M22" s="99"/>
-      <c r="N22" s="99"/>
-      <c r="O22" s="56"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="53"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="63"/>
+      <c r="K22" s="63"/>
+      <c r="L22" s="63"/>
+      <c r="M22" s="63"/>
+      <c r="N22" s="63"/>
+      <c r="O22" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
     <mergeCell ref="R20:T20"/>
     <mergeCell ref="R21:T21"/>
     <mergeCell ref="B3:K3"/>
@@ -2789,15 +2798,12 @@
     <mergeCell ref="R17:T17"/>
     <mergeCell ref="R19:T19"/>
     <mergeCell ref="R18:T18"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="D1:I1"/>
     <mergeCell ref="C9:E9"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="C18:E18"/>
   </mergeCells>
@@ -2844,228 +2850,228 @@
   <sheetData>
     <row r="1" spans="2:41">
       <c r="B1" s="12"/>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="42"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="50"/>
     </row>
     <row r="3" spans="2:41">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="55" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="51"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="57"/>
     </row>
     <row r="5" spans="2:41">
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="2:41" ht="15.6">
-      <c r="B6" s="63" t="s">
+      <c r="B6" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="63" t="s">
+      <c r="C6" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="64" t="s">
+      <c r="D6" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="63" t="s">
+      <c r="E6" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="63"/>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="63"/>
-      <c r="L6" s="63"/>
-      <c r="M6" s="63"/>
-      <c r="N6" s="63"/>
-      <c r="O6" s="63"/>
-      <c r="P6" s="63"/>
-      <c r="Q6" s="63"/>
-      <c r="R6" s="63"/>
-      <c r="S6" s="63"/>
-      <c r="T6" s="63"/>
-      <c r="U6" s="63"/>
-      <c r="V6" s="63"/>
-      <c r="W6" s="63"/>
-      <c r="X6" s="63"/>
-      <c r="Y6" s="63"/>
-      <c r="Z6" s="63"/>
-      <c r="AA6" s="63"/>
-      <c r="AB6" s="63"/>
-      <c r="AC6" s="63"/>
-      <c r="AD6" s="63"/>
-      <c r="AE6" s="63"/>
-      <c r="AF6" s="63"/>
-      <c r="AG6" s="63"/>
-      <c r="AH6" s="63"/>
-      <c r="AI6" s="63"/>
-      <c r="AJ6" s="63"/>
-      <c r="AK6" s="63"/>
-      <c r="AL6" s="63"/>
-      <c r="AM6" s="63"/>
-      <c r="AN6" s="63"/>
-      <c r="AO6" s="63"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
+      <c r="P6" s="67"/>
+      <c r="Q6" s="67"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="67"/>
+      <c r="T6" s="67"/>
+      <c r="U6" s="67"/>
+      <c r="V6" s="67"/>
+      <c r="W6" s="67"/>
+      <c r="X6" s="67"/>
+      <c r="Y6" s="67"/>
+      <c r="Z6" s="67"/>
+      <c r="AA6" s="67"/>
+      <c r="AB6" s="67"/>
+      <c r="AC6" s="67"/>
+      <c r="AD6" s="67"/>
+      <c r="AE6" s="67"/>
+      <c r="AF6" s="67"/>
+      <c r="AG6" s="67"/>
+      <c r="AH6" s="67"/>
+      <c r="AI6" s="67"/>
+      <c r="AJ6" s="67"/>
+      <c r="AK6" s="67"/>
+      <c r="AL6" s="67"/>
+      <c r="AM6" s="67"/>
+      <c r="AN6" s="67"/>
+      <c r="AO6" s="67"/>
     </row>
     <row r="7" spans="2:41" ht="15.6">
-      <c r="B7" s="63"/>
-      <c r="C7" s="63"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="112" t="s">
+      <c r="B7" s="67"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="60" t="s">
+      <c r="F7" s="82" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60"/>
-      <c r="L7" s="60"/>
-      <c r="M7" s="60"/>
-      <c r="N7" s="60"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="60"/>
-      <c r="Q7" s="60"/>
-      <c r="R7" s="60"/>
-      <c r="S7" s="60"/>
-      <c r="T7" s="60"/>
-      <c r="U7" s="60"/>
-      <c r="V7" s="60"/>
-      <c r="W7" s="60"/>
-      <c r="X7" s="60"/>
-      <c r="Y7" s="60"/>
-      <c r="Z7" s="61" t="s">
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="82"/>
+      <c r="K7" s="82"/>
+      <c r="L7" s="82"/>
+      <c r="M7" s="82"/>
+      <c r="N7" s="82"/>
+      <c r="O7" s="82"/>
+      <c r="P7" s="82"/>
+      <c r="Q7" s="82"/>
+      <c r="R7" s="82"/>
+      <c r="S7" s="82"/>
+      <c r="T7" s="82"/>
+      <c r="U7" s="82"/>
+      <c r="V7" s="82"/>
+      <c r="W7" s="82"/>
+      <c r="X7" s="82"/>
+      <c r="Y7" s="82"/>
+      <c r="Z7" s="83" t="s">
         <v>39</v>
       </c>
-      <c r="AA7" s="61"/>
-      <c r="AB7" s="61"/>
-      <c r="AC7" s="61"/>
-      <c r="AD7" s="61"/>
-      <c r="AE7" s="61"/>
-      <c r="AF7" s="61"/>
-      <c r="AG7" s="61"/>
-      <c r="AH7" s="61"/>
-      <c r="AI7" s="62" t="s">
+      <c r="AA7" s="83"/>
+      <c r="AB7" s="83"/>
+      <c r="AC7" s="83"/>
+      <c r="AD7" s="83"/>
+      <c r="AE7" s="83"/>
+      <c r="AF7" s="83"/>
+      <c r="AG7" s="83"/>
+      <c r="AH7" s="83"/>
+      <c r="AI7" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="AJ7" s="62"/>
-      <c r="AK7" s="62"/>
-      <c r="AL7" s="62"/>
-      <c r="AM7" s="62"/>
-      <c r="AN7" s="62"/>
-      <c r="AO7" s="62"/>
+      <c r="AJ7" s="78"/>
+      <c r="AK7" s="78"/>
+      <c r="AL7" s="78"/>
+      <c r="AM7" s="78"/>
+      <c r="AN7" s="78"/>
+      <c r="AO7" s="78"/>
     </row>
     <row r="8" spans="2:41" ht="55.2" customHeight="1">
-      <c r="B8" s="63"/>
-      <c r="C8" s="58" t="s">
+      <c r="B8" s="67"/>
+      <c r="C8" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="58" t="s">
+      <c r="D8" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="113"/>
-      <c r="F8" s="106" t="s">
+      <c r="E8" s="80"/>
+      <c r="F8" s="74" t="s">
         <v>119</v>
       </c>
-      <c r="G8" s="107"/>
-      <c r="H8" s="106" t="s">
+      <c r="G8" s="75"/>
+      <c r="H8" s="74" t="s">
         <v>150</v>
       </c>
-      <c r="I8" s="107"/>
-      <c r="J8" s="106" t="s">
+      <c r="I8" s="75"/>
+      <c r="J8" s="74" t="s">
         <v>149</v>
       </c>
-      <c r="K8" s="107"/>
-      <c r="L8" s="106" t="s">
+      <c r="K8" s="75"/>
+      <c r="L8" s="74" t="s">
         <v>151</v>
       </c>
-      <c r="M8" s="107"/>
-      <c r="N8" s="106" t="s">
+      <c r="M8" s="75"/>
+      <c r="N8" s="74" t="s">
         <v>120</v>
       </c>
-      <c r="O8" s="107"/>
-      <c r="P8" s="106" t="s">
+      <c r="O8" s="75"/>
+      <c r="P8" s="74" t="s">
         <v>152</v>
       </c>
-      <c r="Q8" s="107"/>
-      <c r="R8" s="106" t="s">
+      <c r="Q8" s="75"/>
+      <c r="R8" s="74" t="s">
         <v>153</v>
       </c>
-      <c r="S8" s="107"/>
-      <c r="T8" s="106" t="s">
+      <c r="S8" s="75"/>
+      <c r="T8" s="74" t="s">
         <v>154</v>
       </c>
-      <c r="U8" s="107"/>
-      <c r="V8" s="106" t="s">
+      <c r="U8" s="75"/>
+      <c r="V8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="W8" s="107"/>
-      <c r="X8" s="106" t="s">
+      <c r="W8" s="75"/>
+      <c r="X8" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="Y8" s="107"/>
-      <c r="Z8" s="108" t="s">
+      <c r="Y8" s="75"/>
+      <c r="Z8" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="AA8" s="108" t="s">
+      <c r="AA8" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="AB8" s="108" t="s">
+      <c r="AB8" s="76" t="s">
         <v>32</v>
       </c>
-      <c r="AC8" s="108" t="s">
+      <c r="AC8" s="76" t="s">
         <v>109</v>
       </c>
-      <c r="AD8" s="108" t="s">
+      <c r="AD8" s="76" t="s">
         <v>110</v>
       </c>
-      <c r="AE8" s="108" t="s">
+      <c r="AE8" s="76" t="s">
         <v>111</v>
       </c>
-      <c r="AF8" s="108" t="s">
+      <c r="AF8" s="76" t="s">
         <v>144</v>
       </c>
-      <c r="AG8" s="108" t="s">
+      <c r="AG8" s="76" t="s">
         <v>146</v>
       </c>
-      <c r="AH8" s="108" t="s">
+      <c r="AH8" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="AI8" s="110">
+      <c r="AI8" s="70">
         <v>0</v>
       </c>
-      <c r="AJ8" s="110">
+      <c r="AJ8" s="70">
         <v>1</v>
       </c>
-      <c r="AK8" s="110">
+      <c r="AK8" s="70">
         <v>2</v>
       </c>
-      <c r="AL8" s="110" t="s">
+      <c r="AL8" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="AM8" s="110" t="s">
+      <c r="AM8" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="AN8" s="110" t="s">
+      <c r="AN8" s="70" t="s">
         <v>43</v>
       </c>
-      <c r="AO8" s="110" t="s">
+      <c r="AO8" s="70" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="9" spans="2:41" ht="15.6">
-      <c r="B9" s="63"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="114"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="73"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="81"/>
       <c r="F9" s="13" t="s">
         <v>45</v>
       </c>
@@ -3126,34 +3132,34 @@
       <c r="Y9" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="Z9" s="109"/>
-      <c r="AA9" s="109"/>
-      <c r="AB9" s="109"/>
-      <c r="AC9" s="109"/>
-      <c r="AD9" s="109"/>
-      <c r="AE9" s="109"/>
-      <c r="AF9" s="109"/>
-      <c r="AG9" s="109"/>
-      <c r="AH9" s="109"/>
-      <c r="AI9" s="111"/>
-      <c r="AJ9" s="111"/>
-      <c r="AK9" s="111"/>
-      <c r="AL9" s="111"/>
-      <c r="AM9" s="111"/>
-      <c r="AN9" s="111"/>
-      <c r="AO9" s="111"/>
+      <c r="Z9" s="77"/>
+      <c r="AA9" s="77"/>
+      <c r="AB9" s="77"/>
+      <c r="AC9" s="77"/>
+      <c r="AD9" s="77"/>
+      <c r="AE9" s="77"/>
+      <c r="AF9" s="77"/>
+      <c r="AG9" s="77"/>
+      <c r="AH9" s="77"/>
+      <c r="AI9" s="71"/>
+      <c r="AJ9" s="71"/>
+      <c r="AK9" s="71"/>
+      <c r="AL9" s="71"/>
+      <c r="AM9" s="71"/>
+      <c r="AN9" s="71"/>
+      <c r="AO9" s="71"/>
     </row>
     <row r="10" spans="2:41" ht="15.6">
       <c r="B10" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="103" t="s">
+      <c r="C10" s="43" t="s">
         <v>137</v>
       </c>
-      <c r="D10" s="103" t="s">
+      <c r="D10" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="E10" s="105" t="s">
+      <c r="E10" s="45" t="s">
         <v>138</v>
       </c>
       <c r="F10" s="15" t="s">
@@ -3203,13 +3209,13 @@
       <c r="B11" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="103" t="s">
+      <c r="C11" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="D11" s="104">
+      <c r="D11" s="44">
         <v>0</v>
       </c>
-      <c r="E11" s="105" t="s">
+      <c r="E11" s="45" t="s">
         <v>129</v>
       </c>
       <c r="F11" s="15"/>
@@ -3265,13 +3271,13 @@
       <c r="B12" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="C12" s="103" t="s">
+      <c r="C12" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="D12" s="104">
+      <c r="D12" s="44">
         <v>0</v>
       </c>
-      <c r="E12" s="105" t="s">
+      <c r="E12" s="45" t="s">
         <v>129</v>
       </c>
       <c r="F12" s="15"/>
@@ -3329,13 +3335,13 @@
       <c r="B13" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C13" s="103" t="s">
+      <c r="C13" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="D13" s="103" t="s">
+      <c r="D13" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="E13" s="105" t="s">
+      <c r="E13" s="45" t="s">
         <v>130</v>
       </c>
       <c r="F13" s="15"/>
@@ -3397,13 +3403,13 @@
       <c r="B14" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C14" s="103" t="s">
+      <c r="C14" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="D14" s="103" t="s">
+      <c r="D14" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="E14" s="105" t="s">
+      <c r="E14" s="45" t="s">
         <v>130</v>
       </c>
       <c r="F14" s="15"/>
@@ -3467,13 +3473,13 @@
       <c r="B15" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="103" t="s">
+      <c r="C15" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="D15" s="103" t="s">
+      <c r="D15" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="E15" s="105" t="s">
+      <c r="E15" s="45" t="s">
         <v>130</v>
       </c>
       <c r="F15" s="15"/>
@@ -3539,13 +3545,13 @@
       <c r="B16" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C16" s="103" t="s">
+      <c r="C16" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="D16" s="104">
+      <c r="D16" s="44">
         <v>60</v>
       </c>
-      <c r="E16" s="105" t="s">
+      <c r="E16" s="45" t="s">
         <v>131</v>
       </c>
       <c r="F16" s="15"/>
@@ -3613,13 +3619,13 @@
       <c r="B17" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="C17" s="103" t="s">
+      <c r="C17" s="43" t="s">
         <v>145</v>
       </c>
-      <c r="D17" s="104">
+      <c r="D17" s="44">
         <v>130</v>
       </c>
-      <c r="E17" s="105" t="s">
+      <c r="E17" s="45" t="s">
         <v>156</v>
       </c>
       <c r="F17" s="15"/>
@@ -3687,13 +3693,13 @@
       <c r="B18" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="C18" s="103" t="s">
+      <c r="C18" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="D18" s="104">
+      <c r="D18" s="44">
         <v>237.5</v>
       </c>
-      <c r="E18" s="105" t="s">
+      <c r="E18" s="45" t="s">
         <v>131</v>
       </c>
       <c r="F18" s="15"/>
@@ -3762,6 +3768,28 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="F7:Y7"/>
+    <mergeCell ref="Z7:AH7"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B6:B9"/>
@@ -3778,28 +3806,6 @@
     <mergeCell ref="AD8:AD9"/>
     <mergeCell ref="AI7:AO7"/>
     <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="V8:W8"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="F7:Y7"/>
-    <mergeCell ref="Z7:AH7"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3816,8 +3822,8 @@
   <cols>
     <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="32.6640625" customWidth="1"/>
+    <col min="5" max="5" width="21.109375" customWidth="1"/>
+    <col min="6" max="6" width="43.109375" customWidth="1"/>
     <col min="7" max="7" width="15.88671875" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
     <col min="9" max="9" width="16.109375" bestFit="1" customWidth="1"/>
@@ -3828,46 +3834,46 @@
   <sheetData>
     <row r="1" spans="2:11">
       <c r="B1" s="12"/>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
     </row>
     <row r="3" spans="2:11">
-      <c r="B3" s="86" t="s">
+      <c r="B3" s="99" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="100" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="82" t="s">
+      <c r="C4" s="97" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="95" t="s">
+      <c r="D4" s="108" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="89" t="s">
+      <c r="E4" s="102" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="93"/>
-      <c r="G4" s="89" t="s">
+      <c r="F4" s="106"/>
+      <c r="G4" s="102" t="s">
         <v>53</v>
       </c>
-      <c r="H4" s="90"/>
+      <c r="H4" s="103"/>
     </row>
     <row r="5" spans="2:11" ht="15" thickBot="1">
-      <c r="B5" s="88"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="96"/>
+      <c r="B5" s="101"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="109"/>
       <c r="E5" s="2" t="s">
         <v>157</v>
       </c>
@@ -3885,7 +3891,7 @@
       <c r="B6" s="19">
         <v>9</v>
       </c>
-      <c r="C6" s="91" t="s">
+      <c r="C6" s="104" t="s">
         <v>56</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -3908,7 +3914,7 @@
       <c r="B7" s="19">
         <v>10</v>
       </c>
-      <c r="C7" s="91"/>
+      <c r="C7" s="104"/>
       <c r="D7" s="4" t="s">
         <v>57</v>
       </c>
@@ -3918,10 +3924,10 @@
       <c r="F7" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="G7" s="120">
+      <c r="G7" s="47">
         <v>0</v>
       </c>
-      <c r="H7" s="120">
+      <c r="H7" s="47">
         <v>0</v>
       </c>
     </row>
@@ -3929,7 +3935,7 @@
       <c r="B8" s="19">
         <v>11</v>
       </c>
-      <c r="C8" s="91"/>
+      <c r="C8" s="104"/>
       <c r="D8" s="10" t="s">
         <v>122</v>
       </c>
@@ -3939,10 +3945,10 @@
       <c r="F8" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="G8" s="120">
+      <c r="G8" s="47">
         <v>0</v>
       </c>
-      <c r="H8" s="120">
+      <c r="H8" s="47">
         <v>0</v>
       </c>
     </row>
@@ -3950,7 +3956,7 @@
       <c r="B9" s="19">
         <v>12</v>
       </c>
-      <c r="C9" s="91"/>
+      <c r="C9" s="104"/>
       <c r="D9" s="10" t="s">
         <v>125</v>
       </c>
@@ -3968,86 +3974,86 @@
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="101">
+      <c r="B10" s="41">
         <v>13</v>
       </c>
-      <c r="C10" s="91"/>
-      <c r="D10" s="102" t="s">
+      <c r="C10" s="104"/>
+      <c r="D10" s="42" t="s">
         <v>123</v>
       </c>
       <c r="E10" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F10" s="101" t="s">
+      <c r="F10" s="41" t="s">
         <v>163</v>
       </c>
-      <c r="G10" s="101" t="s">
+      <c r="G10" s="41" t="s">
         <v>168</v>
       </c>
-      <c r="H10" s="101" t="s">
+      <c r="H10" s="41" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="101">
+      <c r="B11" s="41">
         <v>14</v>
       </c>
-      <c r="C11" s="91"/>
-      <c r="D11" s="102" t="s">
+      <c r="C11" s="104"/>
+      <c r="D11" s="42" t="s">
         <v>124</v>
       </c>
       <c r="E11" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F11" s="101" t="s">
+      <c r="F11" s="41" t="s">
         <v>164</v>
       </c>
-      <c r="G11" s="101" t="s">
+      <c r="G11" s="41" t="s">
         <v>168</v>
       </c>
-      <c r="H11" s="101" t="s">
+      <c r="H11" s="41" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="12" spans="2:11">
-      <c r="B12" s="101">
+      <c r="B12" s="41">
         <v>15</v>
       </c>
-      <c r="C12" s="91"/>
-      <c r="D12" s="102" t="s">
+      <c r="C12" s="104"/>
+      <c r="D12" s="42" t="s">
         <v>134</v>
       </c>
       <c r="E12" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F12" s="101" t="s">
+      <c r="F12" s="41" t="s">
         <v>165</v>
       </c>
-      <c r="G12" s="119">
+      <c r="G12" s="46">
         <v>60</v>
       </c>
-      <c r="H12" s="119">
+      <c r="H12" s="46">
         <v>60</v>
       </c>
     </row>
     <row r="13" spans="2:11" ht="14.4" customHeight="1">
-      <c r="B13" s="101">
+      <c r="B13" s="41">
         <v>16</v>
       </c>
-      <c r="C13" s="91"/>
-      <c r="D13" s="102" t="s">
+      <c r="C13" s="104"/>
+      <c r="D13" s="42" t="s">
         <v>135</v>
       </c>
       <c r="E13" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F13" s="101" t="s">
+      <c r="F13" s="41" t="s">
         <v>166</v>
       </c>
-      <c r="G13" s="119">
+      <c r="G13" s="46">
         <v>130</v>
       </c>
-      <c r="H13" s="119">
+      <c r="H13" s="46">
         <v>130</v>
       </c>
     </row>
@@ -4055,7 +4061,7 @@
       <c r="B14" s="2">
         <v>17</v>
       </c>
-      <c r="C14" s="92"/>
+      <c r="C14" s="105"/>
       <c r="D14" s="9" t="s">
         <v>136</v>
       </c>
@@ -4088,121 +4094,121 @@
       <c r="K16" s="21"/>
     </row>
     <row r="17" spans="2:14" ht="15.6" thickTop="1" thickBot="1">
-      <c r="B17" s="66" t="s">
+      <c r="B17" s="86" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="67"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="67"/>
-      <c r="F17" s="97" t="s">
+      <c r="C17" s="87"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="87"/>
+      <c r="F17" s="84" t="s">
         <v>60</v>
       </c>
-      <c r="G17" s="98"/>
-      <c r="H17" s="66" t="s">
+      <c r="G17" s="85"/>
+      <c r="H17" s="86" t="s">
         <v>61</v>
       </c>
-      <c r="I17" s="67"/>
-      <c r="J17" s="67"/>
-      <c r="K17" s="67"/>
-      <c r="L17" s="68"/>
-      <c r="M17" s="73" t="s">
+      <c r="I17" s="87"/>
+      <c r="J17" s="87"/>
+      <c r="K17" s="87"/>
+      <c r="L17" s="88"/>
+      <c r="M17" s="89" t="s">
         <v>62</v>
       </c>
-      <c r="N17" s="74"/>
+      <c r="N17" s="90"/>
     </row>
     <row r="18" spans="2:14" ht="27" customHeight="1" thickTop="1">
-      <c r="B18" s="72" t="s">
+      <c r="B18" s="96" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="76" t="s">
+      <c r="C18" s="113" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="76" t="s">
+      <c r="D18" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="78" t="s">
+      <c r="E18" s="116" t="s">
         <v>66</v>
       </c>
-      <c r="F18" s="80" t="s">
+      <c r="F18" s="98" t="s">
         <v>67</v>
       </c>
-      <c r="G18" s="117" t="s">
+      <c r="G18" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="H18" s="116" t="s">
+      <c r="H18" s="110" t="s">
         <v>69</v>
       </c>
-      <c r="I18" s="115" t="s">
+      <c r="I18" s="112" t="s">
         <v>63</v>
       </c>
-      <c r="J18" s="115" t="s">
+      <c r="J18" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="K18" s="84" t="s">
+      <c r="K18" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="L18" s="69" t="s">
+      <c r="L18" s="93" t="s">
         <v>71</v>
       </c>
-      <c r="M18" s="71" t="s">
+      <c r="M18" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="N18" s="82" t="s">
+      <c r="N18" s="97" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="19" spans="2:14" ht="52.2" customHeight="1">
-      <c r="B19" s="75"/>
-      <c r="C19" s="77"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="79"/>
-      <c r="F19" s="81"/>
-      <c r="G19" s="118"/>
-      <c r="H19" s="83"/>
-      <c r="I19" s="76"/>
-      <c r="J19" s="76"/>
-      <c r="K19" s="85"/>
-      <c r="L19" s="70"/>
-      <c r="M19" s="72"/>
-      <c r="N19" s="80"/>
-    </row>
-    <row r="20" spans="2:14">
+      <c r="B19" s="114"/>
+      <c r="C19" s="115"/>
+      <c r="D19" s="115"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="118"/>
+      <c r="G19" s="120"/>
+      <c r="H19" s="111"/>
+      <c r="I19" s="113"/>
+      <c r="J19" s="113"/>
+      <c r="K19" s="92"/>
+      <c r="L19" s="94"/>
+      <c r="M19" s="96"/>
+      <c r="N19" s="98"/>
+    </row>
+    <row r="20" spans="2:14" ht="33" customHeight="1">
       <c r="B20" s="25">
         <f>9</f>
         <v>9</v>
       </c>
       <c r="C20" s="22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="22">
-        <v>1</v>
-      </c>
-      <c r="E20" s="23">
-        <v>100</v>
-      </c>
-      <c r="F20" s="24">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="F20" s="24" t="s">
+        <v>171</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I20" s="25">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J20" s="22">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K20" s="26">
         <v>0</v>
       </c>
       <c r="L20" s="27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N20" s="28">
         <v>9</v>
@@ -4211,13 +4217,12 @@
     <row r="24" spans="2:14" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="H17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="N18:N19"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B4:B5"/>
@@ -4226,16 +4231,17 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="H17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="N18:N19"/>
     <mergeCell ref="H18:H19"/>
     <mergeCell ref="I18:I19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
     <mergeCell ref="G18:G19"/>
     <mergeCell ref="J18:J19"/>
-    <mergeCell ref="B17:E17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4432,15 +4438,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="301f98df-4edd-4096-94f8-2f8af3eee570">
@@ -4449,6 +4446,15 @@
     <TaxCatchAll xmlns="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4471,14 +4477,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EECFCB93-350B-4228-B7F4-DB12383611F2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA2F5940-EC19-4D08-A8C2-FA31EF734077}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -4487,4 +4485,12 @@
     <ds:schemaRef ds:uri="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EECFCB93-350B-4228-B7F4-DB12383611F2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
+++ b/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
@@ -560,24 +560,6 @@
     <t>F02_P06</t>
   </si>
   <si>
-    <t>1 - 2(T) - 3 - EXIT</t>
-  </si>
-  <si>
-    <t>1 - 2(F) - 3 - 4(T) - 5 - EXIT</t>
-  </si>
-  <si>
-    <t>1 - 2(F) - 3 - 4(F) - 6 - 7(T) - 8(T) - 9 - EXIT</t>
-  </si>
-  <si>
-    <t>1 - 2(F) - 3 - 4(F) - 6 - 7(T) - 8(F) - 10 - 11 - 7(F) - 12(F) - 14 - EXIT</t>
-  </si>
-  <si>
-    <t>1 - 2(F) - 3 - 4(F) - 6 - 7(T) - 8(F) - 10 - 11 - 7(F) - 12(T) - 13 - 14 - EXIT</t>
-  </si>
-  <si>
-    <t>1 - 2(F) - 3 - 4(F) - 6 - 7(T) - 8(F) - 10 - 11 - 7(T) - 8(F) - 10 - 11 - 7(F) - 12(F) - 14 - EXIT</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -750,13 +732,31 @@
     <t>Exception (IAE)</t>
   </si>
   <si>
-    <t>67% line, 100% brach</t>
-  </si>
-  <si>
     <t>nu</t>
   </si>
   <si>
     <t xml:space="preserve">nu am găsit niciun bug în codul funcției </t>
+  </si>
+  <si>
+    <t>67% line, 100% branch</t>
+  </si>
+  <si>
+    <t>START-1 - 2(T) - 3 - EXIT</t>
+  </si>
+  <si>
+    <t>START-1 - 2(F) - 3 - 4(T) - 5 - EXIT</t>
+  </si>
+  <si>
+    <t>START-1 - 2(F) - 3 - 4(F) - 6 - 7(T) - 8(T) - 9 - EXIT</t>
+  </si>
+  <si>
+    <t>START-1 - 2(F) - 3 - 4(F) - 6 - 7(T) - 8(F) - 10 - 11 - 7(F) - 12(F) - 14 - EXIT</t>
+  </si>
+  <si>
+    <t>START-1 - 2(F) - 3 - 4(F) - 6 - 7(T) - 8(F) - 10 - 11 - 7(F) - 12(T) - 13 - 14 - EXIT</t>
+  </si>
+  <si>
+    <t>START-1 - 2(F) - 3 - 4(F) - 6 - 7(T) - 8(F) - 10 - 11 - 7(T) - 8(F) - 10 - 11 - 7(F) - 12(F) - 14 - EXIT</t>
   </si>
 </sst>
 </file>
@@ -1490,7 +1490,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1560,9 +1560,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1620,6 +1617,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1631,9 +1631,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1709,6 +1706,72 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1724,69 +1787,6 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1799,6 +1799,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1809,15 +1815,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1916,6 +1913,108 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>59267</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>33866</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>347133</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>33866</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7137400" y="10117666"/>
+          <a:ext cx="7543800" cy="10058400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>33867</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>33868</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>117710</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>33868</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15705667" y="10117668"/>
+          <a:ext cx="6315310" cy="10058400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100" cap="sq">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="43000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2221,15 +2320,15 @@
   <sheetData>
     <row r="1" spans="2:17">
       <c r="B1" s="12"/>
-      <c r="D1" s="48" t="s">
+      <c r="D1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="50"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="49"/>
     </row>
     <row r="2" spans="2:17">
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="36" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2250,11 +2349,11 @@
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N5" s="33" t="s">
+      <c r="N5" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
     </row>
     <row r="6" spans="2:17">
       <c r="B6" s="1" t="s">
@@ -2324,7 +2423,7 @@
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="2:17">
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="34" t="s">
         <v>82</v>
       </c>
       <c r="C11" s="1"/>
@@ -2375,14 +2474,14 @@
   <sheetData>
     <row r="1" spans="2:20">
       <c r="B1" s="12"/>
-      <c r="D1" s="48" t="s">
+      <c r="D1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="50"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="49"/>
     </row>
     <row r="3" spans="2:20" ht="16.8" customHeight="1">
       <c r="B3" s="55" t="s">
@@ -2399,233 +2498,233 @@
       <c r="K3" s="57"/>
     </row>
     <row r="6" spans="2:20">
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="50"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="49"/>
       <c r="F6" s="29"/>
       <c r="G6" s="29"/>
-      <c r="I6" s="48" t="s">
+      <c r="I6" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="49"/>
-      <c r="N6" s="49"/>
-      <c r="O6" s="49"/>
-      <c r="Q6" s="48" t="s">
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="48"/>
+      <c r="Q6" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49"/>
-      <c r="T6" s="49"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="48"/>
     </row>
     <row r="8" spans="2:20">
       <c r="B8" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="66" t="s">
+      <c r="C8" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
       <c r="F8" s="31"/>
       <c r="G8" s="31"/>
       <c r="I8" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="Q8" s="65" t="s">
+      <c r="Q8" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="R8" s="65"/>
-      <c r="S8" s="65"/>
-      <c r="T8" s="32">
+      <c r="R8" s="64"/>
+      <c r="S8" s="64"/>
+      <c r="T8" s="39">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="2:20">
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="53" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="I9" s="36"/>
-      <c r="Q9" s="65" t="s">
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="I9" s="35"/>
+      <c r="Q9" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="R9" s="65"/>
-      <c r="S9" s="65"/>
-      <c r="T9" s="40" t="s">
+      <c r="R9" s="64"/>
+      <c r="S9" s="64"/>
+      <c r="T9" s="39" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="10" spans="2:20">
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="53" t="s">
         <v>95</v>
       </c>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="I10" s="59" t="s">
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="I10" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="60"/>
-      <c r="K10" s="60"/>
-      <c r="L10" s="60"/>
-      <c r="M10" s="60"/>
-      <c r="N10" s="60"/>
-      <c r="O10" s="61"/>
-      <c r="Q10" s="65" t="s">
+      <c r="J10" s="59"/>
+      <c r="K10" s="59"/>
+      <c r="L10" s="59"/>
+      <c r="M10" s="59"/>
+      <c r="N10" s="59"/>
+      <c r="O10" s="60"/>
+      <c r="Q10" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="R10" s="65" t="s">
+      <c r="R10" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="S10" s="65"/>
-      <c r="T10" s="40" t="s">
+      <c r="S10" s="64"/>
+      <c r="T10" s="39" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="11" spans="2:20">
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="53" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="I11" s="62"/>
-      <c r="J11" s="63"/>
-      <c r="K11" s="63"/>
-      <c r="L11" s="63"/>
-      <c r="M11" s="63"/>
-      <c r="N11" s="63"/>
-      <c r="O11" s="64"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="62"/>
+      <c r="K11" s="62"/>
+      <c r="L11" s="62"/>
+      <c r="M11" s="62"/>
+      <c r="N11" s="62"/>
+      <c r="O11" s="63"/>
     </row>
     <row r="12" spans="2:20">
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="53" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="I12" s="62"/>
-      <c r="J12" s="63"/>
-      <c r="K12" s="63"/>
-      <c r="L12" s="63"/>
-      <c r="M12" s="63"/>
-      <c r="N12" s="63"/>
-      <c r="O12" s="64"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="62"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="62"/>
+      <c r="N12" s="62"/>
+      <c r="O12" s="63"/>
     </row>
     <row r="13" spans="2:20">
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="53" t="s">
         <v>98</v>
       </c>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="63"/>
-      <c r="K13" s="63"/>
-      <c r="L13" s="63"/>
-      <c r="M13" s="63"/>
-      <c r="N13" s="63"/>
-      <c r="O13" s="64"/>
-      <c r="Q13" s="48" t="s">
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="62"/>
+      <c r="K13" s="62"/>
+      <c r="L13" s="62"/>
+      <c r="M13" s="62"/>
+      <c r="N13" s="62"/>
+      <c r="O13" s="63"/>
+      <c r="Q13" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="R13" s="49"/>
-      <c r="S13" s="49"/>
-      <c r="T13" s="49"/>
+      <c r="R13" s="48"/>
+      <c r="S13" s="48"/>
+      <c r="T13" s="48"/>
     </row>
     <row r="14" spans="2:20">
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="63"/>
-      <c r="K14" s="63"/>
-      <c r="L14" s="63"/>
-      <c r="M14" s="63"/>
-      <c r="N14" s="63"/>
-      <c r="O14" s="64"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="62"/>
+      <c r="M14" s="62"/>
+      <c r="N14" s="62"/>
+      <c r="O14" s="63"/>
     </row>
     <row r="15" spans="2:20">
       <c r="B15" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="51" t="s">
+      <c r="C15" s="50" t="s">
         <v>100</v>
       </c>
-      <c r="D15" s="52"/>
-      <c r="E15" s="53"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="63"/>
-      <c r="K15" s="63"/>
-      <c r="L15" s="63"/>
-      <c r="M15" s="63"/>
-      <c r="N15" s="63"/>
-      <c r="O15" s="64"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="52"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="62"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="62"/>
+      <c r="M15" s="62"/>
+      <c r="N15" s="62"/>
+      <c r="O15" s="63"/>
       <c r="Q15" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="R15" s="66" t="s">
+      <c r="R15" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="S15" s="66"/>
-      <c r="T15" s="66"/>
+      <c r="S15" s="65"/>
+      <c r="T15" s="65"/>
     </row>
     <row r="16" spans="2:20">
       <c r="B16" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C16" s="51" t="s">
+      <c r="C16" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="52"/>
-      <c r="E16" s="53"/>
-      <c r="I16" s="62"/>
-      <c r="J16" s="63"/>
-      <c r="K16" s="63"/>
-      <c r="L16" s="63"/>
-      <c r="M16" s="63"/>
-      <c r="N16" s="63"/>
-      <c r="O16" s="64"/>
-      <c r="Q16" s="33" t="s">
+      <c r="D16" s="51"/>
+      <c r="E16" s="52"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="62"/>
+      <c r="K16" s="62"/>
+      <c r="L16" s="62"/>
+      <c r="M16" s="62"/>
+      <c r="N16" s="62"/>
+      <c r="O16" s="63"/>
+      <c r="Q16" s="32" t="s">
         <v>30</v>
       </c>
       <c r="R16" s="54" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="S16" s="54"/>
       <c r="T16" s="54"/>
@@ -2634,23 +2733,23 @@
       <c r="B17" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="51" t="s">
+      <c r="C17" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="D17" s="52"/>
-      <c r="E17" s="53"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="63"/>
-      <c r="K17" s="63"/>
-      <c r="L17" s="63"/>
-      <c r="M17" s="63"/>
-      <c r="N17" s="63"/>
-      <c r="O17" s="64"/>
-      <c r="Q17" s="33" t="s">
+      <c r="D17" s="51"/>
+      <c r="E17" s="52"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="62"/>
+      <c r="K17" s="62"/>
+      <c r="L17" s="62"/>
+      <c r="M17" s="62"/>
+      <c r="N17" s="62"/>
+      <c r="O17" s="63"/>
+      <c r="Q17" s="32" t="s">
         <v>31</v>
       </c>
       <c r="R17" s="54" t="s">
-        <v>113</v>
+        <v>167</v>
       </c>
       <c r="S17" s="54"/>
       <c r="T17" s="54"/>
@@ -2659,23 +2758,23 @@
       <c r="B18" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="51" t="s">
+      <c r="C18" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="D18" s="52"/>
-      <c r="E18" s="53"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="63"/>
-      <c r="K18" s="63"/>
-      <c r="L18" s="63"/>
-      <c r="M18" s="63"/>
-      <c r="N18" s="63"/>
-      <c r="O18" s="64"/>
-      <c r="Q18" s="33" t="s">
+      <c r="D18" s="51"/>
+      <c r="E18" s="52"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="62"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="62"/>
+      <c r="M18" s="62"/>
+      <c r="N18" s="62"/>
+      <c r="O18" s="63"/>
+      <c r="Q18" s="32" t="s">
         <v>32</v>
       </c>
       <c r="R18" s="54" t="s">
-        <v>114</v>
+        <v>168</v>
       </c>
       <c r="S18" s="54"/>
       <c r="T18" s="54"/>
@@ -2684,23 +2783,23 @@
       <c r="B19" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="C19" s="51" t="s">
+      <c r="C19" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="D19" s="52"/>
-      <c r="E19" s="53"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="63"/>
-      <c r="K19" s="63"/>
-      <c r="L19" s="63"/>
-      <c r="M19" s="63"/>
-      <c r="N19" s="63"/>
-      <c r="O19" s="64"/>
-      <c r="Q19" s="33" t="s">
+      <c r="D19" s="51"/>
+      <c r="E19" s="52"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="62"/>
+      <c r="K19" s="62"/>
+      <c r="L19" s="62"/>
+      <c r="M19" s="62"/>
+      <c r="N19" s="62"/>
+      <c r="O19" s="63"/>
+      <c r="Q19" s="32" t="s">
         <v>109</v>
       </c>
       <c r="R19" s="54" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="S19" s="54"/>
       <c r="T19" s="54"/>
@@ -2709,23 +2808,23 @@
       <c r="B20" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="51" t="s">
+      <c r="C20" s="50" t="s">
         <v>105</v>
       </c>
-      <c r="D20" s="52"/>
-      <c r="E20" s="53"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="63"/>
-      <c r="K20" s="63"/>
-      <c r="L20" s="63"/>
-      <c r="M20" s="63"/>
-      <c r="N20" s="63"/>
-      <c r="O20" s="64"/>
-      <c r="Q20" s="33" t="s">
+      <c r="D20" s="51"/>
+      <c r="E20" s="52"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="62"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="62"/>
+      <c r="M20" s="62"/>
+      <c r="N20" s="62"/>
+      <c r="O20" s="63"/>
+      <c r="Q20" s="32" t="s">
         <v>110</v>
       </c>
       <c r="R20" s="54" t="s">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="S20" s="54"/>
       <c r="T20" s="54"/>
@@ -2734,23 +2833,23 @@
       <c r="B21" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="51" t="s">
+      <c r="C21" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="D21" s="52"/>
-      <c r="E21" s="53"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="63"/>
-      <c r="K21" s="63"/>
-      <c r="L21" s="63"/>
-      <c r="M21" s="63"/>
-      <c r="N21" s="63"/>
-      <c r="O21" s="64"/>
-      <c r="Q21" s="33" t="s">
+      <c r="D21" s="51"/>
+      <c r="E21" s="52"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="62"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="62"/>
+      <c r="O21" s="63"/>
+      <c r="Q21" s="32" t="s">
         <v>111</v>
       </c>
       <c r="R21" s="54" t="s">
-        <v>117</v>
+        <v>171</v>
       </c>
       <c r="S21" s="54"/>
       <c r="T21" s="54"/>
@@ -2759,18 +2858,18 @@
       <c r="B22" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="51" t="s">
+      <c r="C22" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="52"/>
-      <c r="E22" s="53"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="63"/>
-      <c r="K22" s="63"/>
-      <c r="L22" s="63"/>
-      <c r="M22" s="63"/>
-      <c r="N22" s="63"/>
-      <c r="O22" s="64"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="52"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="32">
@@ -2850,16 +2949,16 @@
   <sheetData>
     <row r="1" spans="2:41">
       <c r="B1" s="12"/>
-      <c r="D1" s="48" t="s">
+      <c r="D1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="50"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="49"/>
     </row>
     <row r="3" spans="2:41">
       <c r="B3" s="55" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C3" s="56"/>
       <c r="D3" s="56"/>
@@ -2870,208 +2969,208 @@
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="2:41" ht="15.6">
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="67" t="s">
+      <c r="C6" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="67" t="s">
+      <c r="E6" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="67"/>
-      <c r="P6" s="67"/>
-      <c r="Q6" s="67"/>
-      <c r="R6" s="67"/>
-      <c r="S6" s="67"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="67"/>
-      <c r="V6" s="67"/>
-      <c r="W6" s="67"/>
-      <c r="X6" s="67"/>
-      <c r="Y6" s="67"/>
-      <c r="Z6" s="67"/>
-      <c r="AA6" s="67"/>
-      <c r="AB6" s="67"/>
-      <c r="AC6" s="67"/>
-      <c r="AD6" s="67"/>
-      <c r="AE6" s="67"/>
-      <c r="AF6" s="67"/>
-      <c r="AG6" s="67"/>
-      <c r="AH6" s="67"/>
-      <c r="AI6" s="67"/>
-      <c r="AJ6" s="67"/>
-      <c r="AK6" s="67"/>
-      <c r="AL6" s="67"/>
-      <c r="AM6" s="67"/>
-      <c r="AN6" s="67"/>
-      <c r="AO6" s="67"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="66"/>
+      <c r="N6" s="66"/>
+      <c r="O6" s="66"/>
+      <c r="P6" s="66"/>
+      <c r="Q6" s="66"/>
+      <c r="R6" s="66"/>
+      <c r="S6" s="66"/>
+      <c r="T6" s="66"/>
+      <c r="U6" s="66"/>
+      <c r="V6" s="66"/>
+      <c r="W6" s="66"/>
+      <c r="X6" s="66"/>
+      <c r="Y6" s="66"/>
+      <c r="Z6" s="66"/>
+      <c r="AA6" s="66"/>
+      <c r="AB6" s="66"/>
+      <c r="AC6" s="66"/>
+      <c r="AD6" s="66"/>
+      <c r="AE6" s="66"/>
+      <c r="AF6" s="66"/>
+      <c r="AG6" s="66"/>
+      <c r="AH6" s="66"/>
+      <c r="AI6" s="66"/>
+      <c r="AJ6" s="66"/>
+      <c r="AK6" s="66"/>
+      <c r="AL6" s="66"/>
+      <c r="AM6" s="66"/>
+      <c r="AN6" s="66"/>
+      <c r="AO6" s="66"/>
     </row>
     <row r="7" spans="2:41" ht="15.6">
-      <c r="B7" s="67"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="79" t="s">
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="82" t="s">
+      <c r="F7" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="82"/>
-      <c r="H7" s="82"/>
-      <c r="I7" s="82"/>
-      <c r="J7" s="82"/>
-      <c r="K7" s="82"/>
-      <c r="L7" s="82"/>
-      <c r="M7" s="82"/>
-      <c r="N7" s="82"/>
-      <c r="O7" s="82"/>
-      <c r="P7" s="82"/>
-      <c r="Q7" s="82"/>
-      <c r="R7" s="82"/>
-      <c r="S7" s="82"/>
-      <c r="T7" s="82"/>
-      <c r="U7" s="82"/>
-      <c r="V7" s="82"/>
-      <c r="W7" s="82"/>
-      <c r="X7" s="82"/>
-      <c r="Y7" s="82"/>
-      <c r="Z7" s="83" t="s">
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="81"/>
+      <c r="M7" s="81"/>
+      <c r="N7" s="81"/>
+      <c r="O7" s="81"/>
+      <c r="P7" s="81"/>
+      <c r="Q7" s="81"/>
+      <c r="R7" s="81"/>
+      <c r="S7" s="81"/>
+      <c r="T7" s="81"/>
+      <c r="U7" s="81"/>
+      <c r="V7" s="81"/>
+      <c r="W7" s="81"/>
+      <c r="X7" s="81"/>
+      <c r="Y7" s="81"/>
+      <c r="Z7" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="AA7" s="83"/>
-      <c r="AB7" s="83"/>
-      <c r="AC7" s="83"/>
-      <c r="AD7" s="83"/>
-      <c r="AE7" s="83"/>
-      <c r="AF7" s="83"/>
-      <c r="AG7" s="83"/>
-      <c r="AH7" s="83"/>
-      <c r="AI7" s="78" t="s">
+      <c r="AA7" s="82"/>
+      <c r="AB7" s="82"/>
+      <c r="AC7" s="82"/>
+      <c r="AD7" s="82"/>
+      <c r="AE7" s="82"/>
+      <c r="AF7" s="82"/>
+      <c r="AG7" s="82"/>
+      <c r="AH7" s="82"/>
+      <c r="AI7" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="AJ7" s="78"/>
-      <c r="AK7" s="78"/>
-      <c r="AL7" s="78"/>
-      <c r="AM7" s="78"/>
-      <c r="AN7" s="78"/>
-      <c r="AO7" s="78"/>
+      <c r="AJ7" s="77"/>
+      <c r="AK7" s="77"/>
+      <c r="AL7" s="77"/>
+      <c r="AM7" s="77"/>
+      <c r="AN7" s="77"/>
+      <c r="AO7" s="77"/>
     </row>
     <row r="8" spans="2:41" ht="55.2" customHeight="1">
-      <c r="B8" s="67"/>
-      <c r="C8" s="72" t="s">
+      <c r="B8" s="66"/>
+      <c r="C8" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="72" t="s">
+      <c r="D8" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="80"/>
-      <c r="F8" s="74" t="s">
-        <v>119</v>
-      </c>
-      <c r="G8" s="75"/>
-      <c r="H8" s="74" t="s">
-        <v>150</v>
-      </c>
-      <c r="I8" s="75"/>
-      <c r="J8" s="74" t="s">
+      <c r="E8" s="79"/>
+      <c r="F8" s="73" t="s">
+        <v>113</v>
+      </c>
+      <c r="G8" s="74"/>
+      <c r="H8" s="73" t="s">
+        <v>144</v>
+      </c>
+      <c r="I8" s="74"/>
+      <c r="J8" s="73" t="s">
+        <v>143</v>
+      </c>
+      <c r="K8" s="74"/>
+      <c r="L8" s="73" t="s">
+        <v>145</v>
+      </c>
+      <c r="M8" s="74"/>
+      <c r="N8" s="73" t="s">
+        <v>114</v>
+      </c>
+      <c r="O8" s="74"/>
+      <c r="P8" s="73" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q8" s="74"/>
+      <c r="R8" s="73" t="s">
+        <v>147</v>
+      </c>
+      <c r="S8" s="74"/>
+      <c r="T8" s="73" t="s">
+        <v>148</v>
+      </c>
+      <c r="U8" s="74"/>
+      <c r="V8" s="73" t="s">
         <v>149</v>
       </c>
-      <c r="K8" s="75"/>
-      <c r="L8" s="74" t="s">
-        <v>151</v>
-      </c>
-      <c r="M8" s="75"/>
-      <c r="N8" s="74" t="s">
-        <v>120</v>
-      </c>
-      <c r="O8" s="75"/>
-      <c r="P8" s="74" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q8" s="75"/>
-      <c r="R8" s="74" t="s">
-        <v>153</v>
-      </c>
-      <c r="S8" s="75"/>
-      <c r="T8" s="74" t="s">
-        <v>154</v>
-      </c>
-      <c r="U8" s="75"/>
-      <c r="V8" s="74" t="s">
-        <v>155</v>
-      </c>
-      <c r="W8" s="75"/>
-      <c r="X8" s="74" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y8" s="75"/>
-      <c r="Z8" s="76" t="s">
+      <c r="W8" s="74"/>
+      <c r="X8" s="73" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y8" s="74"/>
+      <c r="Z8" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="AA8" s="76" t="s">
+      <c r="AA8" s="75" t="s">
         <v>31</v>
       </c>
-      <c r="AB8" s="76" t="s">
+      <c r="AB8" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="AC8" s="76" t="s">
+      <c r="AC8" s="75" t="s">
         <v>109</v>
       </c>
-      <c r="AD8" s="76" t="s">
+      <c r="AD8" s="75" t="s">
         <v>110</v>
       </c>
-      <c r="AE8" s="76" t="s">
+      <c r="AE8" s="75" t="s">
         <v>111</v>
       </c>
-      <c r="AF8" s="76" t="s">
-        <v>144</v>
-      </c>
-      <c r="AG8" s="76" t="s">
-        <v>146</v>
-      </c>
-      <c r="AH8" s="76" t="s">
-        <v>148</v>
-      </c>
-      <c r="AI8" s="70">
+      <c r="AF8" s="75" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG8" s="75" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH8" s="75" t="s">
+        <v>142</v>
+      </c>
+      <c r="AI8" s="69">
         <v>0</v>
       </c>
-      <c r="AJ8" s="70">
+      <c r="AJ8" s="69">
         <v>1</v>
       </c>
-      <c r="AK8" s="70">
+      <c r="AK8" s="69">
         <v>2</v>
       </c>
-      <c r="AL8" s="70" t="s">
+      <c r="AL8" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="AM8" s="70" t="s">
+      <c r="AM8" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="AN8" s="70" t="s">
+      <c r="AN8" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="AO8" s="70" t="s">
+      <c r="AO8" s="69" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="9" spans="2:41" ht="15.6">
-      <c r="B9" s="67"/>
-      <c r="C9" s="73"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="81"/>
+      <c r="B9" s="66"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="80"/>
       <c r="F9" s="13" t="s">
         <v>45</v>
       </c>
@@ -3084,16 +3183,16 @@
       <c r="I9" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="J9" s="39" t="s">
+      <c r="J9" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="K9" s="39" t="s">
+      <c r="K9" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="L9" s="39" t="s">
+      <c r="L9" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="M9" s="39" t="s">
+      <c r="M9" s="38" t="s">
         <v>46</v>
       </c>
       <c r="N9" s="13" t="s">
@@ -3108,22 +3207,22 @@
       <c r="Q9" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="R9" s="39" t="s">
+      <c r="R9" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="S9" s="39" t="s">
+      <c r="S9" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="T9" s="39" t="s">
+      <c r="T9" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="U9" s="39" t="s">
+      <c r="U9" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="V9" s="39" t="s">
+      <c r="V9" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="39" t="s">
+      <c r="W9" s="38" t="s">
         <v>46</v>
       </c>
       <c r="X9" s="13" t="s">
@@ -3132,38 +3231,38 @@
       <c r="Y9" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="Z9" s="77"/>
-      <c r="AA9" s="77"/>
-      <c r="AB9" s="77"/>
-      <c r="AC9" s="77"/>
-      <c r="AD9" s="77"/>
-      <c r="AE9" s="77"/>
-      <c r="AF9" s="77"/>
-      <c r="AG9" s="77"/>
-      <c r="AH9" s="77"/>
-      <c r="AI9" s="71"/>
-      <c r="AJ9" s="71"/>
-      <c r="AK9" s="71"/>
-      <c r="AL9" s="71"/>
-      <c r="AM9" s="71"/>
-      <c r="AN9" s="71"/>
-      <c r="AO9" s="71"/>
+      <c r="Z9" s="76"/>
+      <c r="AA9" s="76"/>
+      <c r="AB9" s="76"/>
+      <c r="AC9" s="76"/>
+      <c r="AD9" s="76"/>
+      <c r="AE9" s="76"/>
+      <c r="AF9" s="76"/>
+      <c r="AG9" s="76"/>
+      <c r="AH9" s="76"/>
+      <c r="AI9" s="70"/>
+      <c r="AJ9" s="70"/>
+      <c r="AK9" s="70"/>
+      <c r="AL9" s="70"/>
+      <c r="AM9" s="70"/>
+      <c r="AN9" s="70"/>
+      <c r="AO9" s="70"/>
     </row>
     <row r="10" spans="2:41" ht="15.6">
       <c r="B10" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="43" t="s">
-        <v>137</v>
-      </c>
-      <c r="D10" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="E10" s="45" t="s">
-        <v>138</v>
+      <c r="C10" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="E10" s="44" t="s">
+        <v>132</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="G10" s="15"/>
       <c r="H10" s="15"/>
@@ -3185,7 +3284,7 @@
       <c r="X10" s="15"/>
       <c r="Y10" s="15"/>
       <c r="Z10" s="16" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AA10" s="16"/>
       <c r="AB10" s="16"/>
@@ -3196,7 +3295,7 @@
       <c r="AG10" s="16"/>
       <c r="AH10" s="16"/>
       <c r="AI10" s="17" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AJ10" s="17"/>
       <c r="AK10" s="17"/>
@@ -3209,32 +3308,32 @@
       <c r="B11" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="43" t="s">
-        <v>133</v>
-      </c>
-      <c r="D11" s="44">
+      <c r="C11" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11" s="43">
         <v>0</v>
       </c>
-      <c r="E11" s="45" t="s">
-        <v>129</v>
+      <c r="E11" s="44" t="s">
+        <v>123</v>
       </c>
       <c r="F11" s="15"/>
       <c r="G11" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
       <c r="L11" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
       <c r="O11" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="P11" s="15"/>
       <c r="Q11" s="15"/>
@@ -3248,7 +3347,7 @@
       <c r="Y11" s="15"/>
       <c r="Z11" s="16"/>
       <c r="AA11" s="16" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AB11" s="16"/>
       <c r="AC11" s="16"/>
@@ -3258,7 +3357,7 @@
       <c r="AG11" s="16"/>
       <c r="AH11" s="16"/>
       <c r="AI11" s="17" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AJ11" s="17"/>
       <c r="AK11" s="17"/>
@@ -3269,36 +3368,36 @@
     </row>
     <row r="12" spans="2:41" ht="15.6">
       <c r="B12" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="D12" s="44">
+        <v>116</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="D12" s="43">
         <v>0</v>
       </c>
-      <c r="E12" s="45" t="s">
-        <v>129</v>
+      <c r="E12" s="44" t="s">
+        <v>123</v>
       </c>
       <c r="F12" s="15"/>
       <c r="G12" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H12" s="15"/>
       <c r="I12" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="K12" s="15"/>
       <c r="L12" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M12" s="15"/>
       <c r="N12" s="15"/>
       <c r="O12" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="P12" s="15"/>
       <c r="Q12" s="15"/>
@@ -3313,7 +3412,7 @@
       <c r="Z12" s="16"/>
       <c r="AA12" s="16"/>
       <c r="AB12" s="16" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AC12" s="16"/>
       <c r="AD12" s="16"/>
@@ -3322,7 +3421,7 @@
       <c r="AG12" s="16"/>
       <c r="AH12" s="16"/>
       <c r="AI12" s="17" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AJ12" s="17"/>
       <c r="AK12" s="17"/>
@@ -3333,39 +3432,39 @@
     </row>
     <row r="13" spans="2:41" ht="18.600000000000001" customHeight="1">
       <c r="B13" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="C13" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="D13" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="E13" s="45" t="s">
-        <v>130</v>
+        <v>119</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="D13" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13" s="44" t="s">
+        <v>124</v>
       </c>
       <c r="F13" s="15"/>
       <c r="G13" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H13" s="15"/>
       <c r="I13" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="J13" s="15"/>
       <c r="K13" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="L13" s="15"/>
       <c r="M13" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="N13" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="O13" s="15"/>
       <c r="P13" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="Q13" s="15"/>
       <c r="R13" s="15"/>
@@ -3373,7 +3472,7 @@
       <c r="T13" s="15"/>
       <c r="U13" s="15"/>
       <c r="V13" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="W13" s="15"/>
       <c r="X13" s="15"/>
@@ -3382,7 +3481,7 @@
       <c r="AA13" s="16"/>
       <c r="AB13" s="16"/>
       <c r="AC13" s="16" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AD13" s="16"/>
       <c r="AE13" s="16"/>
@@ -3391,7 +3490,7 @@
       <c r="AH13" s="16"/>
       <c r="AI13" s="17"/>
       <c r="AJ13" s="17" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AK13" s="17"/>
       <c r="AL13" s="17"/>
@@ -3401,49 +3500,49 @@
     </row>
     <row r="14" spans="2:41" ht="18" customHeight="1">
       <c r="B14" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C14" s="43" t="s">
-        <v>141</v>
-      </c>
-      <c r="D14" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="E14" s="45" t="s">
-        <v>130</v>
+        <v>117</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="D14" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="E14" s="44" t="s">
+        <v>124</v>
       </c>
       <c r="F14" s="15"/>
       <c r="G14" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H14" s="15"/>
       <c r="I14" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="L14" s="15"/>
       <c r="M14" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="N14" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="O14" s="15"/>
       <c r="P14" s="15"/>
       <c r="Q14" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="R14" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="S14" s="15"/>
       <c r="T14" s="15"/>
       <c r="U14" s="15"/>
       <c r="V14" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="W14" s="15"/>
       <c r="X14" s="15"/>
@@ -3453,7 +3552,7 @@
       <c r="AB14" s="16"/>
       <c r="AC14" s="16"/>
       <c r="AD14" s="16" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AE14" s="16"/>
       <c r="AF14" s="16"/>
@@ -3461,7 +3560,7 @@
       <c r="AH14" s="16"/>
       <c r="AI14" s="17"/>
       <c r="AJ14" s="17" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AK14" s="17"/>
       <c r="AL14" s="17"/>
@@ -3471,51 +3570,51 @@
     </row>
     <row r="15" spans="2:41" ht="18" customHeight="1">
       <c r="B15" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>136</v>
+      </c>
+      <c r="D15" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15" s="44" t="s">
         <v>124</v>
-      </c>
-      <c r="C15" s="43" t="s">
-        <v>142</v>
-      </c>
-      <c r="D15" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="E15" s="45" t="s">
-        <v>130</v>
       </c>
       <c r="F15" s="15"/>
       <c r="G15" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H15" s="15"/>
       <c r="I15" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="J15" s="15"/>
       <c r="K15" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="L15" s="15"/>
       <c r="M15" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="N15" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="O15" s="15"/>
       <c r="P15" s="15"/>
       <c r="Q15" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="R15" s="15"/>
       <c r="S15" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="T15" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="U15" s="15"/>
       <c r="V15" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="W15" s="15"/>
       <c r="X15" s="15"/>
@@ -3526,14 +3625,14 @@
       <c r="AC15" s="16"/>
       <c r="AD15" s="16"/>
       <c r="AE15" s="16" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AF15" s="16"/>
       <c r="AG15" s="16"/>
       <c r="AH15" s="16"/>
       <c r="AI15" s="17"/>
       <c r="AJ15" s="17" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AK15" s="17"/>
       <c r="AL15" s="17"/>
@@ -3543,56 +3642,56 @@
     </row>
     <row r="16" spans="2:41" ht="38.4" customHeight="1">
       <c r="B16" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="C16" s="43" t="s">
-        <v>143</v>
-      </c>
-      <c r="D16" s="44">
+        <v>128</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>137</v>
+      </c>
+      <c r="D16" s="43">
         <v>60</v>
       </c>
-      <c r="E16" s="45" t="s">
-        <v>131</v>
+      <c r="E16" s="44" t="s">
+        <v>125</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="J16" s="15"/>
       <c r="K16" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="L16" s="15"/>
       <c r="M16" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="N16" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="O16" s="15"/>
       <c r="P16" s="15"/>
       <c r="Q16" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="R16" s="15"/>
       <c r="S16" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="T16" s="15"/>
       <c r="U16" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="V16" s="15"/>
       <c r="W16" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="X16" s="15"/>
       <c r="Y16" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="Z16" s="16"/>
       <c r="AA16" s="16"/>
@@ -3601,13 +3700,13 @@
       <c r="AD16" s="16"/>
       <c r="AE16" s="16"/>
       <c r="AF16" s="16" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AG16" s="16"/>
       <c r="AH16" s="16"/>
       <c r="AI16" s="17"/>
       <c r="AJ16" s="17" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AK16" s="17"/>
       <c r="AL16" s="17"/>
@@ -3617,56 +3716,56 @@
     </row>
     <row r="17" spans="2:41" ht="28.2" customHeight="1">
       <c r="B17" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="C17" s="43" t="s">
-        <v>145</v>
-      </c>
-      <c r="D17" s="44">
+        <v>129</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="D17" s="43">
         <v>130</v>
       </c>
-      <c r="E17" s="45" t="s">
-        <v>156</v>
+      <c r="E17" s="44" t="s">
+        <v>150</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H17" s="15"/>
       <c r="I17" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="J17" s="15"/>
       <c r="K17" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="L17" s="15"/>
       <c r="M17" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="N17" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="O17" s="15"/>
       <c r="P17" s="15"/>
       <c r="Q17" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="R17" s="15"/>
       <c r="S17" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="T17" s="15"/>
       <c r="U17" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="V17" s="15"/>
       <c r="W17" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="X17" s="15"/>
       <c r="Y17" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="Z17" s="16"/>
       <c r="AA17" s="16"/>
@@ -3676,13 +3775,13 @@
       <c r="AE17" s="16"/>
       <c r="AF17" s="16"/>
       <c r="AG17" s="16" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AH17" s="16"/>
       <c r="AI17" s="17"/>
       <c r="AJ17" s="17"/>
       <c r="AK17" s="17" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AL17" s="17"/>
       <c r="AM17" s="17"/>
@@ -3691,55 +3790,55 @@
     </row>
     <row r="18" spans="2:41" ht="25.2" customHeight="1">
       <c r="B18" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="C18" s="43" t="s">
-        <v>147</v>
-      </c>
-      <c r="D18" s="44">
+        <v>130</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="43">
         <v>237.5</v>
       </c>
-      <c r="E18" s="45" t="s">
-        <v>131</v>
+      <c r="E18" s="44" t="s">
+        <v>125</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H18" s="15"/>
       <c r="I18" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="J18" s="15"/>
       <c r="K18" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="L18" s="15"/>
       <c r="M18" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="N18" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="O18" s="15"/>
       <c r="P18" s="15"/>
       <c r="Q18" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="R18" s="15"/>
       <c r="S18" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="T18" s="15"/>
       <c r="U18" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="V18" s="15"/>
       <c r="W18" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="X18" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="Y18" s="15"/>
       <c r="Z18" s="16"/>
@@ -3751,11 +3850,11 @@
       <c r="AF18" s="16"/>
       <c r="AG18" s="16"/>
       <c r="AH18" s="16" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AI18" s="17"/>
       <c r="AJ18" s="17" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AK18" s="17"/>
       <c r="AL18" s="17"/>
@@ -3778,16 +3877,16 @@
     <mergeCell ref="H8:I8"/>
     <mergeCell ref="N8:O8"/>
     <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="R8:S8"/>
     <mergeCell ref="AI8:AI9"/>
     <mergeCell ref="Z8:Z9"/>
     <mergeCell ref="AA8:AA9"/>
     <mergeCell ref="AB8:AB9"/>
     <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="V8:W8"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="R8:S8"/>
     <mergeCell ref="AE8:AE9"/>
     <mergeCell ref="AF8:AF9"/>
     <mergeCell ref="D1:G1"/>
@@ -3834,51 +3933,51 @@
   <sheetData>
     <row r="1" spans="2:11">
       <c r="B1" s="12"/>
-      <c r="D1" s="48" t="s">
+      <c r="D1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
     </row>
     <row r="3" spans="2:11">
-      <c r="B3" s="99" t="s">
+      <c r="B3" s="94" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="99"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="94"/>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="100" t="s">
+      <c r="B4" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="97" t="s">
+      <c r="C4" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="108" t="s">
+      <c r="D4" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="102" t="s">
+      <c r="E4" s="97" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="106"/>
-      <c r="G4" s="102" t="s">
+      <c r="F4" s="101"/>
+      <c r="G4" s="97" t="s">
         <v>53</v>
       </c>
-      <c r="H4" s="103"/>
+      <c r="H4" s="98"/>
     </row>
     <row r="5" spans="2:11" ht="15" thickBot="1">
-      <c r="B5" s="101"/>
-      <c r="C5" s="107"/>
-      <c r="D5" s="109"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="104"/>
       <c r="E5" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>54</v>
@@ -3891,43 +3990,43 @@
       <c r="B6" s="19">
         <v>9</v>
       </c>
-      <c r="C6" s="104" t="s">
+      <c r="C6" s="99" t="s">
         <v>56</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>47</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="2:11">
       <c r="B7" s="19">
         <v>10</v>
       </c>
-      <c r="C7" s="104"/>
+      <c r="C7" s="99"/>
       <c r="D7" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="G7" s="47">
+        <v>155</v>
+      </c>
+      <c r="G7" s="46">
         <v>0</v>
       </c>
-      <c r="H7" s="47">
+      <c r="H7" s="46">
         <v>0</v>
       </c>
     </row>
@@ -3935,20 +4034,20 @@
       <c r="B8" s="19">
         <v>11</v>
       </c>
-      <c r="C8" s="104"/>
+      <c r="C8" s="99"/>
       <c r="D8" s="10" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="G8" s="47">
+        <v>156</v>
+      </c>
+      <c r="G8" s="46">
         <v>0</v>
       </c>
-      <c r="H8" s="47">
+      <c r="H8" s="46">
         <v>0</v>
       </c>
     </row>
@@ -3956,104 +4055,104 @@
       <c r="B9" s="19">
         <v>12</v>
       </c>
-      <c r="C9" s="104"/>
+      <c r="C9" s="99"/>
       <c r="D9" s="10" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E9" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11">
+      <c r="B10" s="40">
+        <v>13</v>
+      </c>
+      <c r="C10" s="99"/>
+      <c r="D10" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="F10" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="H10" s="40" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11">
+      <c r="B11" s="40">
+        <v>14</v>
+      </c>
+      <c r="C11" s="99"/>
+      <c r="D11" s="41" t="s">
+        <v>118</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="F11" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="G11" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="H11" s="40" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11">
+      <c r="B12" s="40">
+        <v>15</v>
+      </c>
+      <c r="C12" s="99"/>
+      <c r="D12" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="F12" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="G12" s="45">
+        <v>60</v>
+      </c>
+      <c r="H12" s="45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="14.4" customHeight="1">
+      <c r="B13" s="40">
+        <v>16</v>
+      </c>
+      <c r="C13" s="99"/>
+      <c r="D13" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="F13" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="F9" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11">
-      <c r="B10" s="41">
-        <v>13</v>
-      </c>
-      <c r="C10" s="104"/>
-      <c r="D10" s="42" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="F10" s="41" t="s">
-        <v>163</v>
-      </c>
-      <c r="G10" s="41" t="s">
-        <v>168</v>
-      </c>
-      <c r="H10" s="41" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11">
-      <c r="B11" s="41">
-        <v>14</v>
-      </c>
-      <c r="C11" s="104"/>
-      <c r="D11" s="42" t="s">
-        <v>124</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="F11" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="G11" s="41" t="s">
-        <v>168</v>
-      </c>
-      <c r="H11" s="41" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11">
-      <c r="B12" s="41">
-        <v>15</v>
-      </c>
-      <c r="C12" s="104"/>
-      <c r="D12" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="F12" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="G12" s="46">
-        <v>60</v>
-      </c>
-      <c r="H12" s="46">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" ht="14.4" customHeight="1">
-      <c r="B13" s="41">
-        <v>16</v>
-      </c>
-      <c r="C13" s="104"/>
-      <c r="D13" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="F13" s="41" t="s">
-        <v>166</v>
-      </c>
-      <c r="G13" s="46">
+      <c r="G13" s="45">
         <v>130</v>
       </c>
-      <c r="H13" s="46">
+      <c r="H13" s="45">
         <v>130</v>
       </c>
     </row>
@@ -4061,15 +4160,15 @@
       <c r="B14" s="2">
         <v>17</v>
       </c>
-      <c r="C14" s="105"/>
+      <c r="C14" s="100"/>
       <c r="D14" s="9" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G14" s="2">
         <v>237.5</v>
@@ -4094,30 +4193,30 @@
       <c r="K16" s="21"/>
     </row>
     <row r="17" spans="2:14" ht="15.6" thickTop="1" thickBot="1">
-      <c r="B17" s="86" t="s">
+      <c r="B17" s="107" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="87"/>
-      <c r="D17" s="87"/>
-      <c r="E17" s="87"/>
-      <c r="F17" s="84" t="s">
+      <c r="C17" s="108"/>
+      <c r="D17" s="108"/>
+      <c r="E17" s="108"/>
+      <c r="F17" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="G17" s="85"/>
-      <c r="H17" s="86" t="s">
+      <c r="G17" s="106"/>
+      <c r="H17" s="107" t="s">
         <v>61</v>
       </c>
-      <c r="I17" s="87"/>
-      <c r="J17" s="87"/>
-      <c r="K17" s="87"/>
-      <c r="L17" s="88"/>
-      <c r="M17" s="89" t="s">
+      <c r="I17" s="108"/>
+      <c r="J17" s="108"/>
+      <c r="K17" s="108"/>
+      <c r="L17" s="109"/>
+      <c r="M17" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="N17" s="90"/>
+      <c r="N17" s="84"/>
     </row>
     <row r="18" spans="2:14" ht="27" customHeight="1" thickTop="1">
-      <c r="B18" s="96" t="s">
+      <c r="B18" s="90" t="s">
         <v>63</v>
       </c>
       <c r="C18" s="113" t="s">
@@ -4126,13 +4225,13 @@
       <c r="D18" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="116" t="s">
+      <c r="E18" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="F18" s="98" t="s">
+      <c r="F18" s="92" t="s">
         <v>67</v>
       </c>
-      <c r="G18" s="119" t="s">
+      <c r="G18" s="114" t="s">
         <v>68</v>
       </c>
       <c r="H18" s="110" t="s">
@@ -4144,33 +4243,33 @@
       <c r="J18" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="K18" s="91" t="s">
+      <c r="K18" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="L18" s="93" t="s">
+      <c r="L18" s="87" t="s">
         <v>71</v>
       </c>
-      <c r="M18" s="95" t="s">
+      <c r="M18" s="89" t="s">
         <v>72</v>
       </c>
-      <c r="N18" s="97" t="s">
+      <c r="N18" s="91" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="19" spans="2:14" ht="52.2" customHeight="1">
-      <c r="B19" s="114"/>
-      <c r="C19" s="115"/>
-      <c r="D19" s="115"/>
-      <c r="E19" s="117"/>
-      <c r="F19" s="118"/>
-      <c r="G19" s="120"/>
+      <c r="B19" s="116"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="117"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="115"/>
       <c r="H19" s="111"/>
       <c r="I19" s="113"/>
       <c r="J19" s="113"/>
-      <c r="K19" s="92"/>
-      <c r="L19" s="94"/>
-      <c r="M19" s="96"/>
-      <c r="N19" s="98"/>
+      <c r="K19" s="86"/>
+      <c r="L19" s="88"/>
+      <c r="M19" s="90"/>
+      <c r="N19" s="92"/>
     </row>
     <row r="20" spans="2:14" ht="33" customHeight="1">
       <c r="B20" s="25">
@@ -4184,16 +4283,16 @@
         <v>0</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F20" s="24" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="I20" s="25">
         <v>0</v>
@@ -4208,7 +4307,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="N20" s="28">
         <v>9</v>
@@ -4217,7 +4316,6 @@
     <row r="24" spans="2:14" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B17:E17"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="C18:C19"/>
     <mergeCell ref="D18:D19"/>
@@ -4233,15 +4331,16 @@
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="F17:G17"/>
     <mergeCell ref="H17:L17"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="B17:E17"/>
     <mergeCell ref="M17:N17"/>
     <mergeCell ref="K18:K19"/>
     <mergeCell ref="L18:L19"/>
     <mergeCell ref="M18:M19"/>
     <mergeCell ref="N18:N19"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="J18:J19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
